--- a/Theo_doi_tien_do_boi_thuong_GPMB.xlsx
+++ b/Theo_doi_tien_do_boi_thuong_GPMB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TrongDung\Dropbox\share\webapp\BC dinh ky SNNMT\BoiThuong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E33FC43-F7DC-46B3-BD3C-C4C0EDA0B606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F457342D-999D-4FBA-9764-7E6186FDE598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="610" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="610" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng hợp toàn TP" sheetId="1" r:id="rId1"/>
@@ -279,10 +279,6 @@
 (nếu có)</t>
   </si>
   <si>
-    <t>Chủ đầu tư /
-Đơn vị GPMB</t>
-  </si>
-  <si>
     <t>Địa bàn
 (Phường/Xã)</t>
   </si>
@@ -798,12 +794,6 @@
     <t>Nhập liệu</t>
   </si>
   <si>
-    <t>Quản lý hệ thống</t>
-  </si>
-  <si>
-    <t>Quản lý nhập liệu</t>
-  </si>
-  <si>
     <t>BQLDA.KhuCongNgheCao</t>
   </si>
   <si>
@@ -1558,6 +1548,15 @@
   </si>
   <si>
     <t>Ban QLDA ĐTXD phường Dĩ An</t>
+  </si>
+  <si>
+    <t>Quản trị</t>
+  </si>
+  <si>
+    <t>Quản lý báo cáo</t>
+  </si>
+  <si>
+    <t>Đơn vị GPMB</t>
   </si>
 </sst>
 </file>
@@ -2327,7 +2326,7 @@
       <c r="N2" s="39"/>
       <c r="O2" s="37"/>
     </row>
-    <row r="3" spans="1:31" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -2338,88 +2337,88 @@
         <v>30</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AB3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AC3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AE3" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="AE3" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -2427,19 +2426,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="G4" s="13">
         <v>850000</v>
@@ -2512,13 +2511,13 @@
         <v>91</v>
       </c>
       <c r="AC4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AD4" s="11" t="s">
+      <c r="AE4" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="AE4" s="12" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -2526,17 +2525,17 @@
         <v>2</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" s="13">
         <v>120000</v>
@@ -2609,13 +2608,13 @@
         <v>51</v>
       </c>
       <c r="AC5" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AD5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="AE5" s="12" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -7267,7 +7266,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -7281,7 +7280,7 @@
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -7301,31 +7300,31 @@
         <v>29</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="J4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8267,7 +8266,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -8276,7 +8275,7 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -8288,33 +8287,33 @@
         <v>28</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8322,16 +8321,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8339,16 +8338,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8356,16 +8355,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8373,16 +8372,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8390,16 +8389,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8407,16 +8406,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8424,16 +8423,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8441,16 +8440,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8458,16 +8457,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8475,16 +8474,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8492,16 +8491,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8509,16 +8508,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
@@ -8526,16 +8525,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8543,16 +8542,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8560,16 +8559,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="D20" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -8577,16 +8576,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
@@ -8594,16 +8593,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -8638,16 +8637,16 @@
         <v>28</v>
       </c>
       <c r="B1" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>161</v>
-      </c>
       <c r="D1" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -8655,13 +8654,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>191</v>
-      </c>
       <c r="D2" s="27" t="s">
-        <v>195</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -8669,13 +8668,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>193</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>196</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -8683,16 +8682,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -8700,16 +8699,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -8717,16 +8716,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -8734,16 +8733,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -8751,16 +8750,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -8768,16 +8767,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -8785,16 +8784,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -8802,16 +8801,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -8819,16 +8818,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -8836,16 +8835,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -8853,16 +8852,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -8870,16 +8869,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -8887,16 +8886,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -8904,16 +8903,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -8921,16 +8920,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -8938,16 +8937,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -8955,16 +8954,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -8972,16 +8971,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -8989,16 +8988,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -9006,16 +9005,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -9023,16 +9022,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -9040,16 +9039,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -9057,16 +9056,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -9074,16 +9073,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="C27" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="C27" s="27" t="s">
-        <v>380</v>
-      </c>
       <c r="D27" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -9091,16 +9090,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -9108,16 +9107,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -9125,16 +9124,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -9142,16 +9141,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -9159,16 +9158,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="27" t="s">
         <v>385</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -9176,16 +9175,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -9193,16 +9192,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -9210,16 +9209,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -9227,16 +9226,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -9244,16 +9243,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -9261,16 +9260,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -9278,16 +9277,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -9295,16 +9294,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -9312,16 +9311,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -9329,16 +9328,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -9346,16 +9345,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -9363,16 +9362,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -9380,16 +9379,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -9397,16 +9396,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -9414,16 +9413,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -9431,16 +9430,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -9448,16 +9447,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -9465,16 +9464,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -9506,16 +9505,16 @@
         <v>29</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9523,16 +9522,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -9540,31 +9539,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="34"/>
       <c r="B4" s="25" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -9572,19 +9571,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -9592,19 +9591,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9612,16 +9611,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9629,16 +9628,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9646,16 +9645,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9663,16 +9662,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9680,16 +9679,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9697,16 +9696,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9714,16 +9713,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9731,16 +9730,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9748,16 +9747,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9765,16 +9764,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9782,16 +9781,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9799,16 +9798,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9816,16 +9815,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9833,16 +9832,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9850,16 +9849,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -9867,170 +9866,170 @@
         <v>20</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A23" s="34"/>
       <c r="B23" s="26" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="34"/>
       <c r="B24" s="26" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34"/>
       <c r="B25" s="26" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="34"/>
       <c r="B26" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>433</v>
-      </c>
       <c r="D26" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A27" s="34"/>
       <c r="B27" s="26" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
       <c r="B28" s="26" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="21" x14ac:dyDescent="0.3">
       <c r="A29" s="34"/>
       <c r="B29" s="26" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="34"/>
       <c r="B30" s="26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34"/>
       <c r="B31" s="26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10038,16 +10037,16 @@
         <v>21</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10055,16 +10054,16 @@
         <v>22</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10072,16 +10071,16 @@
         <v>23</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F34" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10089,16 +10088,16 @@
         <v>24</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F35" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10106,16 +10105,16 @@
         <v>25</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10123,16 +10122,16 @@
         <v>26</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10140,16 +10139,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10157,16 +10156,16 @@
         <v>28</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F39" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10174,16 +10173,16 @@
         <v>29</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10191,16 +10190,16 @@
         <v>30</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F41" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10208,16 +10207,16 @@
         <v>31</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10225,16 +10224,16 @@
         <v>32</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10242,16 +10241,16 @@
         <v>33</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10259,16 +10258,16 @@
         <v>34</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10276,16 +10275,16 @@
         <v>35</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10293,16 +10292,16 @@
         <v>36</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10310,16 +10309,16 @@
         <v>37</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10327,16 +10326,16 @@
         <v>38</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F49" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10344,16 +10343,16 @@
         <v>39</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F50" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10361,16 +10360,16 @@
         <v>40</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F51" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10378,32 +10377,32 @@
         <v>41</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F52" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="34"/>
       <c r="B53" s="26" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10411,16 +10410,16 @@
         <v>42</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F54" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10428,16 +10427,16 @@
         <v>43</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F55" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10445,16 +10444,16 @@
         <v>44</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F56" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10462,16 +10461,16 @@
         <v>45</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10479,16 +10478,16 @@
         <v>46</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F58" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10496,16 +10495,16 @@
         <v>47</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10513,16 +10512,16 @@
         <v>48</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F60" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10530,16 +10529,16 @@
         <v>49</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F61" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10547,16 +10546,16 @@
         <v>50</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10564,16 +10563,16 @@
         <v>51</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F63" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10581,16 +10580,16 @@
         <v>52</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F64" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10598,16 +10597,16 @@
         <v>53</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F65" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10615,16 +10614,16 @@
         <v>54</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F66" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10632,16 +10631,16 @@
         <v>55</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F67" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10649,16 +10648,16 @@
         <v>56</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E68" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10666,16 +10665,16 @@
         <v>57</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -10683,32 +10682,32 @@
         <v>58</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E70" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F70" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="34"/>
       <c r="B71" s="26" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C71" s="26"/>
       <c r="D71" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10716,16 +10715,16 @@
         <v>59</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E72" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F72" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10733,16 +10732,16 @@
         <v>60</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10750,16 +10749,16 @@
         <v>61</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10767,16 +10766,16 @@
         <v>62</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E75" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F75" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10784,16 +10783,16 @@
         <v>63</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E76" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10801,16 +10800,16 @@
         <v>64</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10818,16 +10817,16 @@
         <v>65</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10835,16 +10834,16 @@
         <v>66</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -10852,16 +10851,16 @@
         <v>67</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10869,16 +10868,16 @@
         <v>68</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10886,16 +10885,16 @@
         <v>69</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E82" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10903,16 +10902,16 @@
         <v>70</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E83" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10920,16 +10919,16 @@
         <v>71</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E84" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10937,16 +10936,16 @@
         <v>72</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E85" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -10954,16 +10953,16 @@
         <v>73</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -10971,16 +10970,16 @@
         <v>74</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -10988,16 +10987,16 @@
         <v>75</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -11005,16 +11004,16 @@
         <v>76</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11022,16 +11021,16 @@
         <v>77</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11039,16 +11038,16 @@
         <v>78</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11056,16 +11055,16 @@
         <v>79</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D92" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="E92" s="25" t="s">
+        <v>440</v>
+      </c>
+      <c r="F92" s="27" t="s">
         <v>385</v>
-      </c>
-      <c r="E92" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="F92" s="27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11073,16 +11072,16 @@
         <v>80</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F93" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11090,16 +11089,16 @@
         <v>81</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11107,32 +11106,32 @@
         <v>82</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E95" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A96" s="34"/>
       <c r="B96" s="26" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C96" s="26"/>
       <c r="D96" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F96" s="25" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -11140,16 +11139,16 @@
         <v>83</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E97" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="F97" s="25" t="s">
         <v>416</v>
-      </c>
-      <c r="F97" s="25" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11157,16 +11156,16 @@
         <v>84</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11174,17 +11173,17 @@
         <v>85</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C99" s="26"/>
       <c r="D99" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E99" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11192,16 +11191,16 @@
         <v>86</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11209,16 +11208,16 @@
         <v>87</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E101" s="25" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11226,16 +11225,16 @@
         <v>88</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E102" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11243,16 +11242,16 @@
         <v>89</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E103" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11260,16 +11259,16 @@
         <v>90</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11277,16 +11276,16 @@
         <v>91</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F105" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -11294,16 +11293,16 @@
         <v>92</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F106" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11311,16 +11310,16 @@
         <v>93</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F107" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11328,16 +11327,16 @@
         <v>94</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D108" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F108" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11345,16 +11344,16 @@
         <v>95</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D109" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E109" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F109" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11362,16 +11361,16 @@
         <v>96</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D110" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F110" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11379,16 +11378,16 @@
         <v>97</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D111" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E111" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F111" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11396,16 +11395,16 @@
         <v>98</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D112" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E112" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F112" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11413,16 +11412,16 @@
         <v>99</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D113" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F113" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11430,16 +11429,16 @@
         <v>100</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E114" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F114" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11447,16 +11446,16 @@
         <v>101</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E115" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11464,16 +11463,16 @@
         <v>102</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E116" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F116" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11481,16 +11480,16 @@
         <v>103</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F117" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11498,16 +11497,16 @@
         <v>104</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F118" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11515,16 +11514,16 @@
         <v>105</v>
       </c>
       <c r="B119" s="25" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F119" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11532,16 +11531,16 @@
         <v>106</v>
       </c>
       <c r="B120" s="25" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F120" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11549,16 +11548,16 @@
         <v>107</v>
       </c>
       <c r="B121" s="25" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F121" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11566,16 +11565,16 @@
         <v>108</v>
       </c>
       <c r="B122" s="25" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11583,16 +11582,16 @@
         <v>109</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11600,16 +11599,16 @@
         <v>110</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11617,16 +11616,16 @@
         <v>111</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11634,16 +11633,16 @@
         <v>112</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F126" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11651,16 +11650,16 @@
         <v>113</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D127" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E127" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F127" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11668,16 +11667,16 @@
         <v>114</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F128" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11685,16 +11684,16 @@
         <v>115</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F129" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11702,16 +11701,16 @@
         <v>116</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D130" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F130" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11719,16 +11718,16 @@
         <v>117</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F131" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11736,16 +11735,16 @@
         <v>118</v>
       </c>
       <c r="B132" s="25" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F132" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11753,16 +11752,16 @@
         <v>119</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D133" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F133" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11770,16 +11769,16 @@
         <v>120</v>
       </c>
       <c r="B134" s="25" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D134" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F134" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11787,16 +11786,16 @@
         <v>121</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F135" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11804,16 +11803,16 @@
         <v>122</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D136" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E136" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F136" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11821,16 +11820,16 @@
         <v>123</v>
       </c>
       <c r="B137" s="25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D137" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E137" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F137" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11838,16 +11837,16 @@
         <v>124</v>
       </c>
       <c r="B138" s="25" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E138" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F138" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11855,16 +11854,16 @@
         <v>125</v>
       </c>
       <c r="B139" s="25" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F139" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11872,16 +11871,16 @@
         <v>126</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E140" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F140" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -11889,16 +11888,16 @@
         <v>127</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D141" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F141" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11906,16 +11905,16 @@
         <v>128</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D142" s="25" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F142" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11923,16 +11922,16 @@
         <v>129</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D143" s="25" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F143" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11940,16 +11939,16 @@
         <v>130</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E144" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F144" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11957,16 +11956,16 @@
         <v>131</v>
       </c>
       <c r="B145" s="25" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E145" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F145" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11974,16 +11973,16 @@
         <v>132</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E146" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F146" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -11991,16 +11990,16 @@
         <v>133</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E147" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F147" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12008,16 +12007,16 @@
         <v>134</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E148" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F148" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12025,16 +12024,16 @@
         <v>135</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F149" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12042,16 +12041,16 @@
         <v>136</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E150" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F150" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12059,16 +12058,16 @@
         <v>137</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E151" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F151" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12076,16 +12075,16 @@
         <v>138</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E152" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F152" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12093,16 +12092,16 @@
         <v>139</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E153" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F153" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12110,16 +12109,16 @@
         <v>140</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E154" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F154" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12127,16 +12126,16 @@
         <v>141</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D155" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E155" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F155" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12144,16 +12143,16 @@
         <v>142</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D156" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F156" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12161,16 +12160,16 @@
         <v>143</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D157" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E157" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F157" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12178,16 +12177,16 @@
         <v>144</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D158" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E158" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F158" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12195,16 +12194,16 @@
         <v>145</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F159" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -12212,16 +12211,16 @@
         <v>146</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D160" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F160" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12229,16 +12228,16 @@
         <v>147</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D161" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F161" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="21" x14ac:dyDescent="0.3">
@@ -12246,16 +12245,16 @@
         <v>148</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D162" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F162" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
